--- a/diseases/d123/2005-2009.xlsx
+++ b/diseases/d123/2005-2009.xlsx
@@ -2199,7 +2199,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN14" t="b">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -5061,7 +5061,7 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN24" t="b">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -6969,7 +6969,7 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN34" t="b">
@@ -7923,7 +7923,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8877,7 +8877,7 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN44" t="b">
@@ -9831,7 +9831,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10785,7 +10785,7 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN54" t="b">
@@ -11739,7 +11739,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12693,7 +12693,7 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN64" t="b">
@@ -14424,7 +14424,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15523,7 +15523,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -16622,7 +16622,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -17721,7 +17721,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -18820,7 +18820,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -19919,7 +19919,7 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN103" t="b">
@@ -21018,7 +21018,7 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN109" t="b">
@@ -22117,7 +22117,7 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN115" t="b">
@@ -23216,7 +23216,7 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN121" t="b">
@@ -24315,7 +24315,7 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN127" t="b">
@@ -25414,7 +25414,7 @@
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN133" t="b">
@@ -26513,7 +26513,7 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN139" t="b">
@@ -28244,7 +28244,7 @@
       </c>
       <c r="AM148" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN148" t="b">
@@ -29343,7 +29343,7 @@
       </c>
       <c r="AM154" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN154" t="b">
@@ -30442,7 +30442,7 @@
       </c>
       <c r="AM160" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN160" t="b">
@@ -31541,7 +31541,7 @@
       </c>
       <c r="AM166" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN166" t="b">
@@ -32640,7 +32640,7 @@
       </c>
       <c r="AM172" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN172" t="b">
@@ -33739,7 +33739,7 @@
       </c>
       <c r="AM178" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN178" t="b">
@@ -34838,7 +34838,7 @@
       </c>
       <c r="AM184" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN184" t="b">
@@ -35937,7 +35937,7 @@
       </c>
       <c r="AM190" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN190" t="b">
@@ -37036,7 +37036,7 @@
       </c>
       <c r="AM196" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN196" t="b">
@@ -38135,7 +38135,7 @@
       </c>
       <c r="AM202" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN202" t="b">
@@ -39234,7 +39234,7 @@
       </c>
       <c r="AM208" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN208" t="b">
@@ -40333,7 +40333,7 @@
       </c>
       <c r="AM214" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN214" t="b">
@@ -50019,7 +50019,7 @@
       </c>
       <c r="AM263" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN263" t="b">
@@ -52929,7 +52929,7 @@
       </c>
       <c r="AM278" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN278" t="b">
@@ -54028,7 +54028,7 @@
       </c>
       <c r="AM284" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN284" t="b">
@@ -55127,7 +55127,7 @@
       </c>
       <c r="AM290" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN290" t="b">
@@ -56226,7 +56226,7 @@
       </c>
       <c r="AM296" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN296" t="b">
@@ -57325,7 +57325,7 @@
       </c>
       <c r="AM302" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN302" t="b">
@@ -58424,7 +58424,7 @@
       </c>
       <c r="AM308" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN308" t="b">
@@ -59523,7 +59523,7 @@
       </c>
       <c r="AM314" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN314" t="b">
@@ -60622,7 +60622,7 @@
       </c>
       <c r="AM320" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN320" t="b">
@@ -61721,7 +61721,7 @@
       </c>
       <c r="AM326" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN326" t="b">
@@ -62820,7 +62820,7 @@
       </c>
       <c r="AM332" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN332" t="b">
@@ -63919,7 +63919,7 @@
       </c>
       <c r="AM338" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN338" t="b">
@@ -73605,7 +73605,7 @@
       </c>
       <c r="AM387" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN387" t="b">
@@ -76515,7 +76515,7 @@
       </c>
       <c r="AM402" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN402" t="b">
@@ -77614,7 +77614,7 @@
       </c>
       <c r="AM408" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN408" t="b">
@@ -78713,7 +78713,7 @@
       </c>
       <c r="AM414" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN414" t="b">
@@ -79812,7 +79812,7 @@
       </c>
       <c r="AM420" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN420" t="b">
@@ -80911,7 +80911,7 @@
       </c>
       <c r="AM426" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN426" t="b">
@@ -82010,7 +82010,7 @@
       </c>
       <c r="AM432" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN432" t="b">
@@ -83109,7 +83109,7 @@
       </c>
       <c r="AM438" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN438" t="b">
@@ -84208,7 +84208,7 @@
       </c>
       <c r="AM444" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN444" t="b">
@@ -85307,7 +85307,7 @@
       </c>
       <c r="AM450" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN450" t="b">
@@ -86406,7 +86406,7 @@
       </c>
       <c r="AM456" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN456" t="b">
@@ -87505,7 +87505,7 @@
       </c>
       <c r="AM462" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN462" t="b">
